--- a/backend/app/data/rules.xlsx
+++ b/backend/app/data/rules.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Business Rules" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Executable Rules" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,300 +414,4119 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:N76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Rule Id</t>
+          <t>Section</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Rule Name</t>
+          <t>Item</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Analysis</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Trigger Logic</t>
+          <t>Risk Level</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Severity</t>
+          <t>Operational Definition</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Routine</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Medical</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Frequency</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Implementation Status</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Executable Rule Ids</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Executable Flag Columns</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Realtime Supported</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Implementation Notes</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>R006</t>
+          <t>Operational Rules</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Modifier 59 on vision codes</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Modifier 59 appears on a vision exam or material procedure.</t>
+          <t>Coding Violations / Unbundling</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Procedure code begins with 92 or V, and any modifier equals 59.</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Coding Review</t>
+          <t>Review of CMS Correct Coding Edits, Peer-to-Peer  (PTP) and Medically Unlikely Edits (MUE)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Executable</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>R102</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>R102_CCI_Edit</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>POC checks configured same-day CCI conflict pairs; full PTP and MUE edit tables are not loaded.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R007</t>
+          <t>Operational Rules</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>High billed-to-allowed ratio</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>The billed amount is more than twice the eligible amount.</t>
+          <t>Modifier Abuse FWA Pattern</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>AmtEligible is greater than 0 and AmtCharged / AmtEligible is greater than 2.0.</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Billing Concern</t>
+          <t>Bilateral Reimbursement for Status 1 Codes</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Executable</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>R103</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>R103_Bilateral</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>POC flags bilateral, left, and right modifiers; CMS status indicator data is not loaded.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R008</t>
+          <t>Operational Rules</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Excessive units on exam codes</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>More than one unit is allowed on a routine exam code.</t>
+          <t>Unbundling/ FWA Pattern</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ProcedureCode is an exam code and AllowedUnits is greater than 1.</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Coding Review</t>
+          <t>Bilateral procedures submitted twice CPT codes with bilateral indicator = 2</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Executable</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>R103</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>R103_Bilateral</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>POC flags bilateral, left, and right modifiers; bilateral indicator 2 requires CMS fee schedule data.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R009</t>
+          <t>Operational Rules</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Invalid CPT for vision plan</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>The procedure code does not match expected vision plan code families.</t>
+          <t>FWA Pattern</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ProcedureCode does not start with 92 or V.</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Billing Concern</t>
+          <t>Exam Double Billing combination of Optometric Exam (92002, 92012, 92004, 92014, S0620, S0621) same day as E and M (CPT 99201 to 99215)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Executable</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>R100</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>R100_Two_Exams_One_Day</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>POC flags multiple exam codes on the same claim service day; E/M pairing is catalog-only.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R013</t>
+          <t>Operational Rules</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Provider high exam volume</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Provider exam volume is at or above the historical 99th percentile.</t>
+          <t>FWA Pattern</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Provider exam count is greater than or equal to the 99th percentile.</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Provider Pattern</t>
+          <t>CPT Rule Violation, exam following a Comp. Exam CPT 92004/ 92014 followed by CPT (S0620, S0621, 92002, or 92012) or DX H52 or Z010 1 to 5 days following</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Executable</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>R101</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>R101_Exam_After_Comprehensive</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>POC flags comprehensive and routine exams on the same claim service day; the 1-5 day lookback needs member history.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R014</t>
+          <t>Operational Rules</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Provider high material volume</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Provider material volume is at or above the historical 99th percentile.</t>
+          <t>Modifier Abuse FWA Pattern</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Provider material count is greater than or equal to the 99th percentile.</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Provider Pattern</t>
+          <t>Exams same day Global Surgery Periods with or without modifiers</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Catalog Only</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Cataloged from business rules; deterministic implementation requires additional source data or adjudication context.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R015</t>
+          <t>Operational Rules</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Provider high average billed amount</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Provider average billed amount is at or above the historical 99th percentile.</t>
+          <t>Modifier Abuse FWA Pattern</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Provider average AmtCharged is greater than or equal to the 99th percentile.</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Provider Pattern</t>
+          <t>Exams during Global Surgery Periods</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Catalog Only</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Cataloged from business rules; deterministic implementation requires additional source data or adjudication context.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R016</t>
+          <t>Operational Rules</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Provider high add-on usage</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Provider add-on usage ratio is at or above the historical 99th percentile.</t>
+          <t>FWA Pattern</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Provider add-on count divided by material count is greater than or equal to the 99th percentile.</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Provider Pattern</t>
+          <t>Duplicate Claims Search</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Catalog Only</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Cataloged from business rules; deterministic implementation requires additional source data or adjudication context.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Operational Rules</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Unbundling of Exam</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Routine Exam (S0620/ S0621) same day as refraction (92015), refraction is included</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Catalog Only</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Cataloged from business rules; deterministic implementation requires additional source data or adjudication context.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Operational Rules</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>FWA Pattern</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Outlier review statistical review of provider services to the network</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Executable</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>R013, R014, R015, R016</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>R013_Provider_High_Exam_Volume_Flag, R014_Provider_High_Material_Volume_Flag, R015_Provider_High_Avg_Billed_Flag, R016_Provider_High_Addon_Usage_Flag</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Historical POC provider outlier flags cover exam volume, material volume, average billed amount, and add-on usage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Operational Rules</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>FWA Pattern</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Outlier review statistical review of provider exams with and without additional services to the network</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Executable</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>R013</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>R013_Provider_High_Exam_Volume_Flag</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Historical POC flags provider exam volume at or above the 99th percentile.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Operational Rules</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Overutilization</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Frequency  medical optometry procedures to exam frequencies</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Executable</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>R013</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>R013_Provider_High_Exam_Volume_Flag</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Historical POC provider exam volume is a frequency proxy until medical optometry procedure families are modeled.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Operational Rules</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Unbundling of Exam</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Tonometry Service (CPT 92100) same day as an exam, inclusive unless the provider performs the service 3X's</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Catalog Only</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Cataloged from business rules; deterministic implementation requires additional source data or adjudication context.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Operational Rules</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Unbundling of Exam</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Sensory Motor Exams (CPT 92060), inclusive to an exam unless there are clear and specific circumstances to document separately</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Catalog Only</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Cataloged from business rules; deterministic implementation requires additional source data or adjudication context.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Operational Rules</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Unbundling of Exam</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Fundus Photos (92250) and exam frequencies with routine DXs or new patient exams</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Catalog Only</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Cataloged from business rules; deterministic implementation requires additional source data or adjudication context.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Operational Rules</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Unbundling of Exam</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Extended Visual Field Exams (CPT's 92081, 92082, or 92083) inclusive to an exam unless there are clear and specific circumstances to document separately</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Catalog Only</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Cataloged from business rules; deterministic implementation requires additional source data or adjudication context.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Operational Rules</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Unbundling of Exam</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Gonioscopy (CPT's 92020) review to document separately as a separate procedure</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Catalog Only</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Cataloged from business rules; deterministic implementation requires additional source data or adjudication context.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Operational Rules</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>FWA Pattern</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Services submitted with unspecified or other visual disturbances diagnosis codes</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Catalog Only</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Cataloged from business rules; deterministic implementation requires additional source data or adjudication context.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Operational Rules</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>FWA Pattern</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Level 5 Evaluation and Management Exams (CPT 99205, 99215)</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Catalog Only</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Cataloged from business rules; deterministic implementation requires additional source data or adjudication context.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Operational Rules</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>FWA Pattern</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Excessive charges for Medically Necessary contacts</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Executable</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>R007</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>R007_High_Billed_to_Allowed_Flag</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>POC uses billed-to-allowed ratio greater than 2.0 as the current excessive-charge signal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Operational Rules</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>FWA Pattern</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Opticians submitting exams</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Catalog Only</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Cataloged from business rules; deterministic implementation requires additional source data or adjudication context.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Operational Rules</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Coding Violation/ FWA Pattern</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>New Patient for Established Patient exams within 3 years of first new pt exam</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Catalog Only</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Cataloged from business rules; deterministic implementation requires additional source data or adjudication context.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Operational Rules</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Coding Violation/ FWA Pattern</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Vision Therapy (CPT 92065) and exams same day</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Catalog Only</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Cataloged from business rules; deterministic implementation requires additional source data or adjudication context.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Operational Rules</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>FWA Pattern</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Vision Therapy Review (92065) and more than 1 units of service per day</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Executable</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>R008</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>R008_Excessive_Units_Exam_Flag</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>POC flags allowed units greater than 1 on exam codes; the 92065-specific unit rule remains catalog-only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Operational Rules</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>FWA Pattern</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Vision Therapy Review (92065) and/ or Rehabilitation Services (CPT 97's)</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Catalog Only</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Cataloged from business rules; deterministic implementation requires additional source data or adjudication context.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Operational Rules</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>FWA Pattern</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Location of service reviews</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Catalog Only</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Cataloged from business rules; deterministic implementation requires additional source data or adjudication context.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Operational Rules</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>FWA Pattern</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Frequency of contact lens evaluations (CPT 92310) on the same day as eye exam</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Catalog Only</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Cataloged from business rules; deterministic implementation requires additional source data or adjudication context.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Operational Rules</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>FWA Potential</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Submitting the same service under more than one policy (Same member with 2 distinct policies)</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Catalog Only</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Cataloged from business rules; deterministic implementation requires additional source data or adjudication context.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Operational Rules</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>FWA Potential Materials</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Materials dispensed without exams, potential services not rendered</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Catalog Only</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Cataloged from business rules; deterministic implementation requires additional source data or adjudication context.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Operational Rules</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>FWA Potential Materials</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Family Orders, review for member abuse</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Catalog Only</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Cataloged from business rules; deterministic implementation requires additional source data or adjudication context.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Operational Rules</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>FWA Pattern</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Material orders for patients without an exam in the calendar year</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Catalog Only</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Cataloged from business rules; deterministic implementation requires additional source data or adjudication context.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Operational Rules</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>FWA Pattern</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Services provided related to open angle glaucoma diagnosis billing</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Catalog Only</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Cataloged from business rules; deterministic implementation requires additional source data or adjudication context.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Operational Rules</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>FWA Pattern</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Repair Replace same day as new order</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Catalog Only</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Cataloged from business rules; deterministic implementation requires additional source data or adjudication context.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Operational Rules</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>FWA Pattern</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Providers services to patients &lt;&gt; in geographic area</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Catalog Only</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Cataloged from business rules; deterministic implementation requires additional source data or adjudication context.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Operational Rules</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>FWA Pattern</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Providers submitting services from multiple offices on the same day</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Catalog Only</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Cataloged from business rules; deterministic implementation requires additional source data or adjudication context.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Operational Rules</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Fraud</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Charging members for RXs</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Catalog Only</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Cataloged from business rules; deterministic implementation requires additional source data or adjudication context.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Operational Rules</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>FWA Pattern</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Provider utilization of routine vision diagnosis vs medical diagnosis codes</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Catalog Only</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Cataloged from business rules; deterministic implementation requires additional source data or adjudication context.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Operational Rules</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Modifier Abuse FWA Pattern</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Exams and Medical Optometry procedures with modifier 59 (Docs vs. Techs)</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Executable</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>R006</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>R006_Modifier59_Flag</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>POC flags modifier 59 on vision exam or material procedure codes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Operational Rules</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Abuse Pattern</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Exams with modifier 25 for the same service (Drug Treatments) on multiple visits</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Catalog Only</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Cataloged from business rules; deterministic implementation requires additional source data or adjudication context.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Operational Rules</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>FWA Internal</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Member and out of network payments (Direct Service Adjustments)</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Catalog Only</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Cataloged from business rules; deterministic implementation requires additional source data or adjudication context.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Operational Rules</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>FWA Potential Materials</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Materials: Practitioner Private Sale and submits claims</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Catalog Only</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Cataloged from business rules; deterministic implementation requires additional source data or adjudication context.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Operational Rules</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>FWA Potential Materials</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Billing Sunglasses when not available as a member benefit V2020 with V2744</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Catalog Only</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Cataloged from business rules; deterministic implementation requires additional source data or adjudication context.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Operational Rules</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>FWA Potential Materials</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Frequency of Repair and Replace, review for member or provider abuse</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Catalog Only</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Cataloged from business rules; deterministic implementation requires additional source data or adjudication context.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Operational Rules</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>FWA Potential Materials</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Providers billing on same day over multiple years</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Catalog Only</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Cataloged from business rules; deterministic implementation requires additional source data or adjudication context.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Operational Rules</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>FWA Pattern Surgery</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Eye lash removal (CPT 67820) splitting individual eye services after the 10 day rule</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Catalog Only</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Cataloged from business rules; deterministic implementation requires additional source data or adjudication context.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Operational Rules</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>FWA Pattern Surgery</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Punctal Plugs (CPT 68761) splitting individual eye services after the 10 day rule</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Catalog Only</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Cataloged from business rules; deterministic implementation requires additional source data or adjudication context.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Operational Rules</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>FWA Pattern Surgery</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Surgery; Cataract Surgery with additional procedures (MIG)</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Catalog Only</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Cataloged from business rules; deterministic implementation requires additional source data or adjudication context.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Operational Rules</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>FWA Pattern Surgery</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Surgery; Cataract Surgery, Major CPT (66982) v Minor (66984), Simple v Extensive</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Catalog Only</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>Cataloged from business rules; deterministic implementation requires additional source data or adjudication context.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Operational Rules</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>FWA Pattern Surgery</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Surgery sessions (61793,66762,67109,67141,67145,67208,67210,67218,67220,67229,G0185,G0186,G0187,G0251,G0340,G0424)</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Catalog Only</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Cataloged from business rules; deterministic implementation requires additional source data or adjudication context.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Operational Rules</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>FWA Pattern Surgery</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Surgery; Frequency of multiple YAG laser sessions (CPT 66821)</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Catalog Only</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Cataloged from business rules; deterministic implementation requires additional source data or adjudication context.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Operational Rules</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>FWA Pattern Surgery</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Surgery: Injections with no Jcodes (11900, 64612) potential cosmetic injections (Collagen, Botox)</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Catalog Only</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>Cataloged from business rules; deterministic implementation requires additional source data or adjudication context.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Operational Rules</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>FWA Pattern Surgery</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Surgery; Multiple Stage billing (CPT 66802,66821,66840,66915,66982,66983,66984,67031,67102,67103,67104,67106,67113,67971,67973,67974,67975)</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Catalog Only</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Cataloged from business rules; deterministic implementation requires additional source data or adjudication context.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Operational Rules</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>FWA Pattern Drugs</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Drugs, High Cost and Frequency of treatments (CPT J0178, J2778, J9035, J2503)</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Catalog Only</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>Cataloged from business rules; deterministic implementation requires additional source data or adjudication context.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Operational Rules</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>FWA Pattern Drugs</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Drugs; Botox (CPT 64612 &amp; C9018, C9278, J0585, J0586, J0587, J0588, J0860, J1155, Q2040) for non-spasm related DX's</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Catalog Only</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Cataloged from business rules; deterministic implementation requires additional source data or adjudication context.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Operational Rules</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>FWA Pattern Labs</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Labs; (CPT 83861 &amp; CLIA Waiver) or Tear Analysis</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Catalog Only</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>Cataloged from business rules; deterministic implementation requires additional source data or adjudication context.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Operational Rules</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>FWA Pattern Surgery</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Surgery: Trichiasis (67825) cosmetic vs. medically necessary</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Catalog Only</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>Cataloged from business rules; deterministic implementation requires additional source data or adjudication context.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Operational Rules</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>FWA Pattern Surgery</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Surgery: Blepharoplasty (15823, 67904) cosmetic vs. medically necessary</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Catalog Only</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>Cataloged from business rules; deterministic implementation requires additional source data or adjudication context.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Operational Rules</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Upcoding Materials</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Material Upcoding, Polycarb (V2763/ 4)</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Catalog Only</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>Cataloged from business rules; deterministic implementation requires additional source data or adjudication context.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Operational Rules</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Upcoding Materials</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Material Upcoding, V2700 thru V2799 compared to population</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Catalog Only</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>Cataloged from business rules; deterministic implementation requires additional source data or adjudication context.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Operational Rules</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Upcoding Materials</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Material Upcoding, Single (V21X) vs Bifocal (V22X) vs Trifocal (V23X)</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Catalog Only</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>Cataloged from business rules; deterministic implementation requires additional source data or adjudication context.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Operational Rules</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>FWA Potential</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Blind Services (ICD-10 H54.*)</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Catalog Only</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>Cataloged from business rules; deterministic implementation requires additional source data or adjudication context.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Operational Rules</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>FWA Potential</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Lasik then glasses or contacts</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Catalog Only</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>Cataloged from business rules; deterministic implementation requires additional source data or adjudication context.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Operational Rules</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>FWA Potential</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Out of Network reimbursement to In Network Providers</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Catalog Only</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>Cataloged from business rules; deterministic implementation requires additional source data or adjudication context.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Operational Rules</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>FWA Potential</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Age related Diagnosis review</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Catalog Only</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>Cataloged from business rules; deterministic implementation requires additional source data or adjudication context.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Operational Rules</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>FWA Potential</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Standard vs Oversize frame (V2020 v V2025)</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Catalog Only</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>Cataloged from business rules; deterministic implementation requires additional source data or adjudication context.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Shared Client Risks</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>FWA Potential</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Exam Double Billing, exams services submitted to both Versant Health and Medical plans for the same patient on the same day</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Executable</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>R100</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>R100_Two_Exams_One_Day</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>POC flags duplicate exam combinations within current claim-day data; cross-plan matching requires medical plan feeds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Shared Client Risks</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>FWA Potential</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Contracted versant Health providers submitting routine services to Medical</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Catalog Only</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>Cataloged from business rules; deterministic implementation requires additional source data or adjudication context.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Shared Client Risks</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>FWA Potential</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Refractions billed to Medical plans for Versant Health Routine Exams</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Catalog Only</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>Cataloged from business rules; deterministic implementation requires additional source data or adjudication context.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Shared Client Risks</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>FWA Potential</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Review of Medical Plan services to Versant analytics</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Catalog Only</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>Cataloged from business rules; deterministic implementation requires additional source data or adjudication context.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Shared Client Risks</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>FWA Potential</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Exams provided during Global Surgery Periods</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Catalog Only</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>Cataloged from business rules; deterministic implementation requires additional source data or adjudication context.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Shared Client Risks</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>FWA Potential</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Surgeries, Major v Minor, Simple v Extensive</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Catalog Only</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>Cataloged from business rules; deterministic implementation requires additional source data or adjudication context.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>CMS</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>CMS</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Multiple Payment Reduction (MPR)</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Catalog Only</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>Cataloged from business rules; deterministic implementation requires additional source data or adjudication context.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>CMS</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>CMS</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Telehealth</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Catalog Only</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>Cataloged from business rules; deterministic implementation requires additional source data or adjudication context.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>CMS</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>CMS</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Pandemic Billing</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>Catalog Only</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>Cataloged from business rules; deterministic implementation requires additional source data or adjudication context.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>CMS</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>CMS</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>PPE</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Catalog Only</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>Cataloged from business rules; deterministic implementation requires additional source data or adjudication context.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Rule Id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Rule Name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Trigger Logic</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Realtime Supported</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>R006</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Modifier 59 on vision codes</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Modifier 59 appears on a vision exam or material procedure.</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Procedure code begins with 92 or V, and any modifier equals 59.</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Coding Review</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>R007</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>High billed-to-allowed ratio</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>The billed amount is more than twice the eligible amount.</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>AmtEligible is greater than 0 and AmtCharged / AmtEligible is greater than 2.0.</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Billing Concern</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>R008</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Excessive units on exam codes</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>More than one unit is allowed on a routine exam code.</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>ProcedureCode is an exam code and AllowedUnits is greater than 1.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Coding Review</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>R009</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Invalid CPT for vision plan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>The procedure code does not match expected vision plan code families.</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>ProcedureCode does not start with 92 or V.</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Billing Concern</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>R013</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Provider high exam volume</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Provider exam volume is at or above the historical 99th percentile.</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Provider exam count is greater than or equal to the 99th percentile.</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Provider Pattern</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>R014</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Provider high material volume</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Provider material volume is at or above the historical 99th percentile.</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Provider material count is greater than or equal to the 99th percentile.</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Provider Pattern</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>R015</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Provider high average billed amount</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Provider average billed amount is at or above the historical 99th percentile.</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Provider average AmtCharged is greater than or equal to the 99th percentile.</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Provider Pattern</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>R016</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Provider high add-on usage</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Provider add-on usage ratio is at or above the historical 99th percentile.</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Provider add-on count divided by material count is greater than or equal to the 99th percentile.</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Provider Pattern</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>R017</t>
         </is>
       </c>
@@ -733,6 +4553,159 @@
       <c r="F10" t="inlineStr">
         <is>
           <t>Documentation Gap</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>R100</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Two exams in one day</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>More than one distinct eye exam code appears on the same claim service day.</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Same ClaimId and ServiceDate contains more than one distinct exam code.</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Utilization Pattern</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>R101</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Exam after comprehensive</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>A routine exam appears on the same claim service day as a comprehensive exam.</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Same ClaimId and ServiceDate contains a comprehensive exam and a routine exam.</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Utilization Pattern</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>R102</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>CCI edit conflict</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Procedure codes on the same claim service day appear in a known CCI conflict pair.</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Same ClaimId and ServiceDate contains one of the configured CCI code pairs.</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Coding Review</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>R103</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Bilateral modifier</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>A bilateral or left/right modifier appears on the claim line.</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Modifier, Modifier2, or Modifier3 is 50, LT, or RT.</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Coding Review</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
